--- a/XBRL-template-MPERS/Group/05-SOCI-BeforeTax.xlsx
+++ b/XBRL-template-MPERS/Group/05-SOCI-BeforeTax.xlsx
@@ -691,10 +691,26 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Total comprehensive income</t>
-        </is>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>*Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="B28">
+        <f>1*B27+1*B11</f>
+        <v/>
+      </c>
+      <c r="C28">
+        <f>1*C27+1*C11</f>
+        <v/>
+      </c>
+      <c r="D28">
+        <f>1*D27+1*D11</f>
+        <v/>
+      </c>
+      <c r="E28">
+        <f>1*E27+1*E11</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -725,19 +741,19 @@
         </is>
       </c>
       <c r="B32">
-        <f>1*B27+1*B30+1*B11+1*B31</f>
+        <f>1*B30+1*B31</f>
         <v/>
       </c>
       <c r="C32">
-        <f>1*C27+1*C30+1*C11+1*C31</f>
+        <f>1*C30+1*C31</f>
         <v/>
       </c>
       <c r="D32">
-        <f>1*D27+1*D30+1*D11+1*D31</f>
+        <f>1*D30+1*D31</f>
         <v/>
       </c>
       <c r="E32">
-        <f>1*E27+1*E30+1*E11+1*E31</f>
+        <f>1*E30+1*E31</f>
         <v/>
       </c>
     </row>

--- a/XBRL-template-MPERS/Group/05-SOCI-BeforeTax.xlsx
+++ b/XBRL-template-MPERS/Group/05-SOCI-BeforeTax.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -470,290 +470,255 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Disclosure on statement of comprehensive income before tax [abstract]</t>
+          <t>Disclosure on statement of comprehensive income before tax</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Comprehensive income before tax [abstract]</t>
+          <t>Comprehensive income before tax</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Statement of comprehensive income before tax [table]</t>
+          <t>Statement of comprehensive income</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Consolidated and separate financial statements [axis]</t>
+          <t>Profit (loss)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Group [member]</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Company [member]</t>
+          <t>Components of other comprehensive income that will not be reclassified to profit or loss, before tax</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Statement of comprehensive income before tax [line items]</t>
+          <t>Other comprehensive income, before tax, exchange differences on translation</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Statement of comprehensive income [abstract]</t>
+          <t>Other comprehensive income, before tax, actuarial gains (losses) on defined benefit plans</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Profit (loss)</t>
+          <t>Other comprehensive income, before tax, gains (losses) on revaluation</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Other comprehensive income [abstract]</t>
+          <t>Share of other comprehensive income of associates and joint ventures accounted for using equity method</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Components of other comprehensive income that will not be reclassified to profit or loss, before tax [abstract]</t>
-        </is>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>*Total other comprehensive income that will not be reclassified to profit or loss, before tax</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>1*B9+1*B10+1*B11+1*B12</f>
+        <v/>
+      </c>
+      <c r="C13">
+        <f>1*C9+1*C10+1*C11+1*C12</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>1*D9+1*D10+1*D11+1*D12</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>1*E9+1*E10+1*E11+1*E12</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Other comprehensive income, before tax, exchange differences on translation</t>
+          <t>Components of other comprehensive income that will be reclassified to profit or loss, before tax</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Other comprehensive income, before tax, actuarial gains (losses) on defined benefit plans</t>
+          <t>Other comprehensive income, before tax, exchange differences on translation</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Other comprehensive income, before tax, gains (losses) on revaluation</t>
+          <t>Other comprehensive income, before tax, change in fair value of hedging instrument</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of other comprehensive income of associates and joint ventures accounted for using equity method</t>
+          <t>Share of other comprehensive income of associates and joint ventures accounted for using equity method, before tax</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>*Total other comprehensive income that will not be reclassified to profit or loss, before tax</t>
+          <t>*Total other comprehensive income that will be reclassified to profit or loss, before tax</t>
         </is>
       </c>
       <c r="B18">
-        <f>1*B14+1*B15+1*B16+1*B17</f>
+        <f>1*B15+1*B16+1*B17</f>
         <v/>
       </c>
       <c r="C18">
-        <f>1*C14+1*C15+1*C16+1*C17</f>
+        <f>1*C15+1*C16+1*C17</f>
         <v/>
       </c>
       <c r="D18">
-        <f>1*D14+1*D15+1*D16+1*D17</f>
+        <f>1*D15+1*D16+1*D17</f>
         <v/>
       </c>
       <c r="E18">
-        <f>1*E14+1*E15+1*E16+1*E17</f>
+        <f>1*E15+1*E16+1*E17</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Components of other comprehensive income that will be reclassified to profit or loss, before tax [abstract]</t>
+          <t>Aggregated income tax relating to components of other comprehensive income that will not be reclassified to profit or loss</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Other comprehensive income, before tax, exchange differences on translation</t>
+          <t>Aggregated income tax relating to components of other comprehensive income that will be reclassified to profit or loss</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Other comprehensive income, before tax, change in fair value of hedging instrument</t>
+          <t>Other comprehensive income before tax gains (losses) on other items</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Share of other comprehensive income of associates and joint ventures accounted for using equity method, before tax</t>
-        </is>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>*Total other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B22">
+        <f>1*B13+1*B18+-1*B19+-1*B20</f>
+        <v/>
+      </c>
+      <c r="C22">
+        <f>1*C13+1*C18+-1*C19+-1*C20</f>
+        <v/>
+      </c>
+      <c r="D22">
+        <f>1*D13+1*D18+-1*D19+-1*D20</f>
+        <v/>
+      </c>
+      <c r="E22">
+        <f>1*E13+1*E18+-1*E19+-1*E20</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>*Total other comprehensive income that will be reclassified to profit or loss, before tax</t>
+          <t>*Total comprehensive income</t>
         </is>
       </c>
       <c r="B23">
-        <f>1*B20+1*B21+1*B22</f>
+        <f>1*B22+1*B6</f>
         <v/>
       </c>
       <c r="C23">
-        <f>1*C20+1*C21+1*C22</f>
+        <f>1*C22+1*C6</f>
         <v/>
       </c>
       <c r="D23">
-        <f>1*D20+1*D21+1*D22</f>
+        <f>1*D22+1*D6</f>
         <v/>
       </c>
       <c r="E23">
-        <f>1*E20+1*E21+1*E22</f>
+        <f>1*E22+1*E6</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Aggregated income tax relating to components of other comprehensive income that will not be reclassified to profit or loss</t>
+          <t>Comprehensive income attributable to</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aggregated income tax relating to components of other comprehensive income that will be reclassified to profit or loss</t>
+          <t>Comprehensive income, attributable to owners of parent</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Other comprehensive income before tax gains (losses) on other items</t>
+          <t>Comprehensive income, attributable to non-controlling interests</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>*Total other comprehensive income</t>
+          <t>*Total comprehensive income</t>
         </is>
       </c>
       <c r="B27">
-        <f>1*B18+1*B23+-1*B24+-1*B25</f>
+        <f>1*B25+1*B26</f>
         <v/>
       </c>
       <c r="C27">
-        <f>1*C18+1*C23+-1*C24+-1*C25</f>
+        <f>1*C25+1*C26</f>
         <v/>
       </c>
       <c r="D27">
-        <f>1*D18+1*D23+-1*D24+-1*D25</f>
+        <f>1*D25+1*D26</f>
         <v/>
       </c>
       <c r="E27">
-        <f>1*E18+1*E23+-1*E24+-1*E25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>*Total comprehensive income</t>
-        </is>
-      </c>
-      <c r="B28">
-        <f>1*B27+1*B11</f>
-        <v/>
-      </c>
-      <c r="C28">
-        <f>1*C27+1*C11</f>
-        <v/>
-      </c>
-      <c r="D28">
-        <f>1*D27+1*D11</f>
-        <v/>
-      </c>
-      <c r="E28">
-        <f>1*E27+1*E11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Comprehensive income attributable to [abstract]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Comprehensive income, attributable to owners of parent</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Comprehensive income, attributable to non-controlling interests</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>*Total comprehensive income</t>
-        </is>
-      </c>
-      <c r="B32">
-        <f>1*B30+1*B31</f>
-        <v/>
-      </c>
-      <c r="C32">
-        <f>1*C30+1*C31</f>
-        <v/>
-      </c>
-      <c r="D32">
-        <f>1*D30+1*D31</f>
-        <v/>
-      </c>
-      <c r="E32">
-        <f>1*E30+1*E31</f>
+        <f>1*E25+1*E26</f>
         <v/>
       </c>
     </row>

--- a/XBRL-template-MPERS/Group/05-SOCI-BeforeTax.xlsx
+++ b/XBRL-template-MPERS/Group/05-SOCI-BeforeTax.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,14 +27,24 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF1F3864"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +59,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -475,14 +486,14 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Comprehensive income before tax</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Statement of comprehensive income</t>
         </is>
@@ -496,14 +507,14 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Other comprehensive income</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Components of other comprehensive income that will not be reclassified to profit or loss, before tax</t>
         </is>
@@ -538,7 +549,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>*Total other comprehensive income that will not be reclassified to profit or loss, before tax</t>
         </is>
@@ -561,7 +572,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>Components of other comprehensive income that will be reclassified to profit or loss, before tax</t>
         </is>
@@ -589,7 +600,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>*Total other comprehensive income that will be reclassified to profit or loss, before tax</t>
         </is>
@@ -633,7 +644,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>*Total other comprehensive income</t>
         </is>
@@ -656,7 +667,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>*Total comprehensive income</t>
         </is>
@@ -679,7 +690,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>Comprehensive income attributable to</t>
         </is>
@@ -700,7 +711,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>*Total comprehensive income</t>
         </is>
